--- a/Models/CDGP.xlsx
+++ b/Models/CDGP.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36a87f973740ffce/Documents/Personal/Education/1_Greenwich/FINA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36a87f973740ffce/Documents/Personal/Finance/Models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="952" documentId="8_{AB677FD1-DACE-674B-8687-43CC81DC24D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8065DC67-CD99-DD4F-801D-7384CB85BAC4}"/>
+  <xr:revisionPtr revIDLastSave="1028" documentId="8_{AB677FD1-DACE-674B-8687-43CC81DC24D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80B655D2-84CF-754B-B191-140FDA80FC6D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17860" xr2:uid="{D13D7BE5-6829-5F46-8F18-3C3B077CFA17}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
-    <sheet name="Definitions" sheetId="3" r:id="rId3"/>
+    <sheet name="WACC" sheetId="4" r:id="rId3"/>
+    <sheet name="Definitions" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="198">
   <si>
     <t xml:space="preserve">Price </t>
   </si>
@@ -543,6 +544,96 @@
   </si>
   <si>
     <t>IPO: Dec 2023</t>
+  </si>
+  <si>
+    <t>Cost of Debt = (Total Interest Expense / Total Debt) x (1 - Tax Rate)</t>
+  </si>
+  <si>
+    <t>Total Debt = Short-Term Debt + Long-Term Debt</t>
+  </si>
+  <si>
+    <t>10y UK bonds yield</t>
+  </si>
+  <si>
+    <t>FTSE100 10y avg</t>
+  </si>
+  <si>
+    <t>Pre-tax Cost of Debt = Interest Expense / Total Debt</t>
+  </si>
+  <si>
+    <t>Market premium</t>
+  </si>
+  <si>
+    <t>Total debt</t>
+  </si>
+  <si>
+    <t>Debt / Equity (D/E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Equity = Risk free rate + stock beta * (Market Risk Premium) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Equity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk free rate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Tax Rate = Income Tax Expense / Earnings Before Taxes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market return </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Debt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC = (E/V * Re) + (D/V * Rd * (1-Tc)) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest expense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E = total value of company's equity = market cap </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective tax rate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D = total value of a debt = Total Debt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V = E + D </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re = Cost of Equity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industry average </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rd = Cost of Debt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tc = Tax Rate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total assets </t>
+  </si>
+  <si>
+    <t>S/E</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* low WACC &amp; the D/E = industry average </t>
   </si>
 </sst>
 </file>
@@ -552,7 +643,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -596,6 +687,32 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="ArialMT"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ArialMT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -656,7 +773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -691,6 +808,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -718,6 +840,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -734,6 +862,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1079,11 +1211,11 @@
       <c r="B4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="26"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
@@ -1210,7 +1342,7 @@
         <v>131</v>
       </c>
       <c r="K15" s="7">
-        <f>Model!E20</f>
+        <f>Model!E21</f>
         <v>1527.3530000000014</v>
       </c>
       <c r="L15" s="21" t="s">
@@ -1228,12 +1360,12 @@
       </c>
     </row>
     <row r="18" spans="2:13">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
       <c r="J18" t="s">
         <v>7</v>
       </c>
@@ -1256,6 +1388,16 @@
       <c r="B20" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="J20" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="K20" s="7">
+        <f>Model!F44</f>
+        <v>58365.641000000003</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
@@ -1271,12 +1413,12 @@
         <f>(C21-D21)/D21</f>
         <v>-7.5323313526738905E-2</v>
       </c>
-      <c r="J21" t="s">
-        <v>94</v>
-      </c>
-      <c r="K21" s="3">
-        <f>Model!F39</f>
-        <v>31544.155000000002</v>
+      <c r="J21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" s="7">
+        <f>Model!F55</f>
+        <v>25714.046000000002</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>6</v>
@@ -1296,15 +1438,12 @@
         <f t="shared" ref="E22:E26" si="0">(C22-D22)/D22</f>
         <v>-3.7169406719085057E-2</v>
       </c>
-      <c r="J22" t="s">
-        <v>106</v>
-      </c>
-      <c r="K22" s="3">
-        <f>Model!F48</f>
-        <v>15396.417000000001</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>6</v>
+      <c r="J22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K22" s="7">
+        <f>K20-K21</f>
+        <v>32651.595000000001</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -1321,13 +1460,6 @@
         <f t="shared" si="0"/>
         <v>0.22318271119842828</v>
       </c>
-      <c r="J23" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K23" s="7">
-        <f>K21-K22</f>
-        <v>16147.738000000001</v>
-      </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
@@ -1343,6 +1475,16 @@
         <f t="shared" si="0"/>
         <v>-0.70886075949367089</v>
       </c>
+      <c r="J24" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="3">
+        <f>Model!F40</f>
+        <v>31544.155000000002</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
@@ -1359,14 +1501,14 @@
         <v>-8.8888888888888892E-2</v>
       </c>
       <c r="J25" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="4">
-        <f>Model!F37/Model!F43</f>
-        <v>0.45502231355601835</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="K25" s="3">
+        <f>Model!F49</f>
+        <v>15396.417000000001</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="2:13">
@@ -1385,22 +1527,13 @@
         <f t="shared" si="0"/>
         <v>-4.9415731643509098E-2</v>
       </c>
-      <c r="J26" t="s">
-        <v>127</v>
-      </c>
-      <c r="K26" s="4">
-        <f>Model!F38/Model!F43</f>
-        <v>6.861096582491058E-2</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="J26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="7">
+        <f>K24-K25</f>
+        <v>16147.738000000001</v>
+      </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="6" t="s">
@@ -1408,17 +1541,16 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
-      <c r="J28" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="K28" s="11">
-        <f>Model!F54/Model!F43</f>
-        <v>0.44056821032771665</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="M28" s="6"/>
+      <c r="J28" t="s">
+        <v>126</v>
+      </c>
+      <c r="K28" s="4">
+        <f>Model!F38/Model!F44</f>
+        <v>0.45502231355601835</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
@@ -1435,14 +1567,14 @@
         <v>-0.19435215946843853</v>
       </c>
       <c r="J29" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K29" s="4">
-        <f>Model!F54/Model!F56</f>
-        <v>0.78752802121917787</v>
+        <f>Model!F39/Model!F44</f>
+        <v>6.861096582491058E-2</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -1459,16 +1591,10 @@
         <f t="shared" ref="E30:E36" si="1">(C30-D30)/D30</f>
         <v>0.15928369462770972</v>
       </c>
-      <c r="J30" t="s">
-        <v>138</v>
-      </c>
-      <c r="K30" s="4">
-        <f>Model!F56/Model!F43</f>
-        <v>0.55943178967228335</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="8" t="s">
@@ -1484,6 +1610,17 @@
         <f t="shared" si="1"/>
         <v>-0.1</v>
       </c>
+      <c r="J31" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K31" s="11">
+        <f>Model!F55/Model!F44</f>
+        <v>0.44056821032771665</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="M31" s="6"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="8" t="s">
@@ -1500,14 +1637,14 @@
         <v>0.22312703583061888</v>
       </c>
       <c r="J32" t="s">
-        <v>128</v>
-      </c>
-      <c r="K32" s="9">
-        <f>K15/AVERAGE(Model!C43:F43)</f>
-        <v>3.2652892550543225E-2</v>
+        <v>137</v>
+      </c>
+      <c r="K32" s="4">
+        <f>Model!F55/Model!F57</f>
+        <v>0.78752802121917787</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -1525,14 +1662,14 @@
         <v>-4.0000000000000001E-3</v>
       </c>
       <c r="J33" t="s">
-        <v>129</v>
-      </c>
-      <c r="K33" s="9">
-        <f>K15/AVERAGE(Model!C56:F56)</f>
-        <v>4.6800885322030548E-2</v>
+        <v>138</v>
+      </c>
+      <c r="K33" s="4">
+        <f>Model!F57/Model!F44</f>
+        <v>0.55943178967228335</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -1566,11 +1703,15 @@
         <f t="shared" si="1"/>
         <v>-4.9415731643509098E-2</v>
       </c>
-      <c r="J35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K35" s="20" t="s">
-        <v>140</v>
+      <c r="J35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K35" s="9">
+        <f>K15/AVERAGE(Model!C44:F44)</f>
+        <v>3.2652892550543225E-2</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -1587,14 +1728,32 @@
         <f t="shared" si="1"/>
         <v>0.11593947923997185</v>
       </c>
+      <c r="J36" t="s">
+        <v>129</v>
+      </c>
+      <c r="K36" s="9">
+        <f>K15/AVERAGE(Model!C57:F57)</f>
+        <v>4.6800885322030548E-2</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="J38" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="26"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="31"/>
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="6" t="s">
@@ -1727,7 +1886,7 @@
     <mergeCell ref="J4:L4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K35" r:id="rId1" xr:uid="{D23C92F1-6734-7D46-B7EE-D4E07767F0D7}"/>
+    <hyperlink ref="K38" r:id="rId1" xr:uid="{D23C92F1-6734-7D46-B7EE-D4E07767F0D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1735,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F056EB-D32B-4A4E-9457-6171B32FD3F2}">
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
@@ -1768,13 +1927,13 @@
       </c>
     </row>
     <row r="3" spans="1:6" customFormat="1">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" spans="1:6" s="7" customFormat="1">
       <c r="A4" s="6"/>
@@ -2022,7 +2181,7 @@
         <v>510.51299999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="B17" t="s">
         <v>82</v>
       </c>
@@ -2039,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="7" customFormat="1">
+    <row r="18" spans="1:7" s="7" customFormat="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
         <v>68</v>
@@ -2061,7 +2220,7 @@
         <v>-1400.3790000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="B19" t="s">
         <v>69</v>
       </c>
@@ -2079,394 +2238,399 @@
         <v>-91.738</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="7" customFormat="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="1:7">
+      <c r="B20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="9">
+        <f t="shared" ref="C20:E20" si="1">C19/C18</f>
+        <v>-0.26103580780950958</v>
+      </c>
+      <c r="D20" s="9">
+        <f t="shared" si="1"/>
+        <v>0.33456558184563079</v>
+      </c>
+      <c r="E20" s="9">
+        <f t="shared" si="1"/>
+        <v>0.33798457474797627</v>
+      </c>
+      <c r="F20" s="9">
+        <f>F19/F18</f>
+        <v>6.5509408524406607E-2</v>
+      </c>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" s="7" customFormat="1">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C21" s="7">
         <f>C18-C19</f>
         <v>1388.8089999999988</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D21" s="7">
         <f>D18-D19</f>
         <v>1053.0319999999974</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E21" s="7">
         <f>E18-E19</f>
         <v>1527.3530000000014</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F21" s="7">
         <f>F18-F19</f>
         <v>-1308.6410000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="B22" t="s">
+    <row r="22" spans="1:7">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="3">
-        <f>C23*C20*100</f>
+      <c r="C23" s="3">
+        <f>C24*C21*100</f>
         <v>131936.85499999986</v>
       </c>
-      <c r="D22" s="3">
-        <f>D23*D20*100</f>
+      <c r="D23" s="3">
+        <f>D24*D21*100</f>
         <v>100038.03999999975</v>
       </c>
-      <c r="E22" s="3">
-        <f>E23*E20*100</f>
+      <c r="E23" s="3">
+        <f>E24*E21*100</f>
         <v>145098.53500000012</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F23" s="3">
         <f>Main!K6</f>
         <v>171520</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" t="s">
+    <row r="24" spans="1:7">
+      <c r="B24" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C24" s="4">
         <v>0.95</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D24" s="4">
         <v>0.95</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E24" s="4">
         <v>0.95</v>
       </c>
-      <c r="F23" s="4">
-        <f>F20/F22*100</f>
+      <c r="F24" s="4">
+        <f>F21/F23*100</f>
         <v>-0.76296700093283587</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" t="s">
+    <row r="25" spans="1:7">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C26" s="9">
         <f>C9/C4</f>
         <v>0.42354517474129172</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D26" s="9">
         <f>D9/D4</f>
         <v>0.48097371396292959</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E26" s="9">
         <f>E9/E4</f>
         <v>0.4425628545549557</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F26" s="9">
         <f>F9/F4</f>
         <v>0.39901529141859232</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="B26" t="s">
+    <row r="27" spans="1:7">
+      <c r="B27" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C27" s="9">
         <f>C14/C4</f>
         <v>6.7693496679814724E-2</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D27" s="9">
         <f>D14/D4</f>
         <v>9.5830843746395097E-2</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E27" s="9">
         <f>E14/E4</f>
         <v>0.12182297950669506</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F27" s="9">
         <f>F14/F4</f>
         <v>-4.5432831560984883E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="B27" t="s">
+    <row r="28" spans="1:7">
+      <c r="B28" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="9">
-        <f>C20/C4</f>
+      <c r="C28" s="9">
+        <f>C21/C4</f>
         <v>8.346265614215477E-2</v>
       </c>
-      <c r="D27" s="9">
-        <f>D20/D4</f>
+      <c r="D28" s="9">
+        <f>D21/D4</f>
         <v>5.9340519760947667E-2</v>
       </c>
-      <c r="E27" s="9">
-        <f>E20/E4</f>
+      <c r="E28" s="9">
+        <f>E21/E4</f>
         <v>7.5853914195329358E-2</v>
       </c>
-      <c r="F27" s="9">
-        <f>F20/F4</f>
+      <c r="F28" s="9">
+        <f>F21/F4</f>
         <v>-6.5943587597712988E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="B29" t="s">
+    <row r="29" spans="1:7">
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D30" s="9">
         <f>D4/C4-1</f>
         <v>6.644853615274382E-2</v>
       </c>
-      <c r="E29" s="9">
-        <f t="shared" ref="E29:F29" si="1">E4/D4-1</f>
+      <c r="E30" s="9">
+        <f t="shared" ref="E30:F30" si="2">E4/D4-1</f>
         <v>0.13467426059479282</v>
       </c>
-      <c r="F29" s="9">
-        <f t="shared" si="1"/>
+      <c r="F30" s="9">
+        <f t="shared" si="2"/>
         <v>-1.4432155341518538E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="B30" t="s">
+    <row r="31" spans="1:7">
+      <c r="B31" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D31" s="9">
         <f>D14/C14-1</f>
         <v>0.50972645888005408</v>
       </c>
-      <c r="E30" s="9">
-        <f t="shared" ref="E30:F30" si="2">E14/D14-1</f>
+      <c r="E31" s="9">
+        <f t="shared" ref="E31:F31" si="3">E14/D14-1</f>
         <v>0.44243120264099334</v>
-      </c>
-      <c r="F30" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.3675590439472947</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="9">
-        <f>D20/C20-1</f>
-        <v>-0.24177334680290929</v>
-      </c>
-      <c r="E31" s="9">
-        <f t="shared" ref="E31:F31" si="3">E20/D20-1</f>
-        <v>0.45043360505664132</v>
       </c>
       <c r="F31" s="9">
         <f t="shared" si="3"/>
+        <v>-1.3675590439472947</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="9">
+        <f>D21/C21-1</f>
+        <v>-0.24177334680290929</v>
+      </c>
+      <c r="E32" s="9">
+        <f t="shared" ref="E32:F32" si="4">E21/D21-1</f>
+        <v>0.45043360505664132</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="4"/>
         <v>-1.8568032406391966</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="7" customFormat="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="30" t="s">
+    <row r="36" spans="1:6" s="7" customFormat="1">
+      <c r="A36" s="6"/>
+      <c r="B36" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="32"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="3">
-        <v>9215</v>
-      </c>
-      <c r="D36" s="3">
-        <v>5801</v>
-      </c>
-      <c r="E36" s="3">
-        <v>1004.3049999999999</v>
-      </c>
-      <c r="F36" s="3">
-        <v>981.96299999999997</v>
-      </c>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="37"/>
     </row>
     <row r="37" spans="1:6">
       <c r="B37" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C37" s="3">
-        <v>12579</v>
+        <v>9215</v>
       </c>
       <c r="D37" s="3">
-        <v>15394</v>
+        <v>5801</v>
       </c>
       <c r="E37" s="3">
-        <v>22581.263999999999</v>
+        <v>1004.3049999999999</v>
       </c>
       <c r="F37" s="3">
-        <v>26557.669000000002</v>
+        <v>981.96299999999997</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="3">
+        <v>12579</v>
+      </c>
+      <c r="D38" s="3">
+        <v>15394</v>
+      </c>
+      <c r="E38" s="3">
+        <v>22581.263999999999</v>
+      </c>
+      <c r="F38" s="3">
+        <v>26557.669000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C39" s="3">
         <v>1309</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D39" s="3">
         <v>2695</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E39" s="3">
         <v>3593.348</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F39" s="3">
         <v>4004.5230000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="7" customFormat="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6" t="s">
+    <row r="40" spans="1:6" s="7" customFormat="1">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="7">
-        <f>SUM(C36:C38)</f>
+      <c r="C40" s="7">
+        <f>SUM(C37:C39)</f>
         <v>23103</v>
       </c>
-      <c r="D39" s="7">
-        <f>SUM(D36:D38)</f>
+      <c r="D40" s="7">
+        <f>SUM(D37:D39)</f>
         <v>23890</v>
       </c>
-      <c r="E39" s="7">
-        <f>SUM(E36:E38)</f>
+      <c r="E40" s="7">
+        <f>SUM(E37:E39)</f>
         <v>27178.917000000001</v>
       </c>
-      <c r="F39" s="7">
-        <f>SUM(F36:F38)</f>
+      <c r="F40" s="7">
+        <f>SUM(F37:F39)</f>
         <v>31544.155000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="3">
-        <v>117</v>
-      </c>
-      <c r="D40" s="3">
-        <v>79</v>
-      </c>
-      <c r="E40" s="3">
-        <v>41.802999999999997</v>
-      </c>
-      <c r="F40" s="3">
-        <v>18.303000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="3">
+        <v>117</v>
+      </c>
+      <c r="D41" s="3">
+        <v>79</v>
+      </c>
+      <c r="E41" s="3">
+        <v>41.802999999999997</v>
+      </c>
+      <c r="F41" s="3">
+        <v>18.303000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C42" s="3">
         <v>14578</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D42" s="3">
         <v>15850</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E42" s="3">
         <v>23898.348000000002</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F42" s="3">
         <v>26803.183000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="18" customFormat="1">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8" t="s">
+    <row r="43" spans="1:6" s="18" customFormat="1">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="18">
-        <f>SUM(C40:C41)</f>
+      <c r="C43" s="18">
+        <f>SUM(C41:C42)</f>
         <v>14695</v>
       </c>
-      <c r="D42" s="18">
-        <f>SUM(D40:D41)</f>
+      <c r="D43" s="18">
+        <f>SUM(D41:D42)</f>
         <v>15929</v>
       </c>
-      <c r="E42" s="18">
-        <f>SUM(E40:E41)</f>
+      <c r="E43" s="18">
+        <f>SUM(E41:E42)</f>
         <v>23940.151000000002</v>
       </c>
-      <c r="F42" s="18">
-        <f>SUM(F40:F41)</f>
+      <c r="F43" s="18">
+        <f>SUM(F41:F42)</f>
         <v>26821.486000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="7" customFormat="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6" t="s">
+    <row r="44" spans="1:6" s="7" customFormat="1">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="7">
-        <f>C42+C39</f>
+      <c r="C44" s="7">
+        <f>C43+C40</f>
         <v>37798</v>
       </c>
-      <c r="D43" s="7">
-        <f>D42+D39</f>
+      <c r="D44" s="7">
+        <f>D43+D40</f>
         <v>39819</v>
       </c>
-      <c r="E43" s="7">
-        <f>E42+E39</f>
+      <c r="E44" s="7">
+        <f>E43+E40</f>
         <v>51119.067999999999</v>
       </c>
-      <c r="F43" s="7">
-        <f>F42+F39</f>
+      <c r="F44" s="7">
+        <f>F43+F40</f>
         <v>58365.641000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-    </row>
     <row r="45" spans="1:6">
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="D45" s="3">
-        <v>4755</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2240.748</v>
-      </c>
-      <c r="F45" s="3">
-        <v>9975.6830000000009</v>
-      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:6">
       <c r="B46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C46" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>4755</v>
       </c>
       <c r="E46" s="3">
-        <v>5748.5709999999999</v>
+        <v>2240.748</v>
       </c>
       <c r="F46" s="3">
-        <v>5044.2839999999997</v>
+        <v>9975.6830000000009</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="B47" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C47" s="3">
         <v>0</v>
@@ -2475,63 +2639,63 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>5748.5709999999999</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5044.2839999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
         <v>430.65499999999997</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F48" s="3">
         <v>376.45</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="7" customFormat="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6" t="s">
+    <row r="49" spans="1:6" s="7" customFormat="1">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="7">
-        <f>SUM(C45:C47)</f>
+      <c r="C49" s="7">
+        <f>SUM(C46:C48)</f>
         <v>4200</v>
       </c>
-      <c r="D48" s="7">
-        <f>SUM(D45:D47)</f>
+      <c r="D49" s="7">
+        <f>SUM(D46:D48)</f>
         <v>4755</v>
       </c>
-      <c r="E48" s="7">
-        <f>SUM(E45:E47)</f>
+      <c r="E49" s="7">
+        <f>SUM(E46:E48)</f>
         <v>8419.9740000000002</v>
       </c>
-      <c r="F48" s="7">
-        <f>SUM(F45:F47)</f>
+      <c r="F49" s="7">
+        <f>SUM(F46:F48)</f>
         <v>15396.417000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="B49" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="3">
-        <v>2482</v>
-      </c>
-      <c r="D49" s="3">
-        <v>2089</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="B50" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C50" s="3">
+        <v>2482</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2089</v>
+      </c>
+      <c r="E50" s="3">
         <v>0</v>
-      </c>
-      <c r="D50" s="3">
-        <v>0</v>
-      </c>
-      <c r="E50" s="3">
-        <v>22.63</v>
       </c>
       <c r="F50" s="3">
         <v>0</v>
@@ -2539,7 +2703,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="B51" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C51" s="3">
         <v>0</v>
@@ -2548,476 +2712,493 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <v>7457.14</v>
+        <v>22.63</v>
       </c>
       <c r="F51" s="3">
-        <v>9225.616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="B52" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C52" s="3">
         <v>0</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7457.14</v>
+      </c>
+      <c r="F52" s="3">
+        <v>9225.616</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="B53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="3">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3">
         <v>528</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E53" s="3">
         <v>893.39700000000005</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F53" s="3">
         <v>1092.0129999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:6" s="18" customFormat="1">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8" t="s">
+    <row r="54" spans="1:6" s="18" customFormat="1">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="18">
-        <f>SUM(C49:C52)</f>
+      <c r="C54" s="18">
+        <f>SUM(C50:C53)</f>
         <v>2482</v>
       </c>
-      <c r="D53" s="18">
-        <f>SUM(D49:D52)</f>
+      <c r="D54" s="18">
+        <f>SUM(D50:D53)</f>
         <v>2617</v>
       </c>
-      <c r="E53" s="18">
-        <f>SUM(E49:E52)</f>
+      <c r="E54" s="18">
+        <f>SUM(E50:E53)</f>
         <v>8373.1670000000013</v>
       </c>
-      <c r="F53" s="18">
-        <f>SUM(F49:F52)</f>
+      <c r="F54" s="18">
+        <f>SUM(F50:F53)</f>
         <v>10317.629000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:6" s="7" customFormat="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6" t="s">
+    <row r="55" spans="1:6" s="7" customFormat="1">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="7">
-        <f>C53+C48</f>
+      <c r="C55" s="7">
+        <f>C54+C49</f>
         <v>6682</v>
       </c>
-      <c r="D54" s="7">
-        <f>D53+D48</f>
+      <c r="D55" s="7">
+        <f>D54+D49</f>
         <v>7372</v>
       </c>
-      <c r="E54" s="7">
-        <f>E53+E48</f>
+      <c r="E55" s="7">
+        <f>E54+E49</f>
         <v>16793.141000000003</v>
       </c>
-      <c r="F54" s="7">
-        <f>F53+F48</f>
+      <c r="F55" s="7">
+        <f>F54+F49</f>
         <v>25714.046000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
     <row r="56" spans="1:6">
-      <c r="B56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C56" s="3">
-        <f>C43-C54</f>
-        <v>31116</v>
-      </c>
-      <c r="D56" s="3">
-        <f>D43-D54</f>
-        <v>32447</v>
-      </c>
-      <c r="E56" s="3">
-        <f>E43-E54</f>
-        <v>34325.926999999996</v>
-      </c>
-      <c r="F56" s="3">
-        <f>F43-F54</f>
-        <v>32651.595000000001</v>
-      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:6">
       <c r="B57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="3">
+        <f>C44-C55</f>
+        <v>31116</v>
+      </c>
+      <c r="D57" s="3">
+        <f>D44-D55</f>
+        <v>32447</v>
+      </c>
+      <c r="E57" s="3">
+        <f>E44-E55</f>
+        <v>34325.926999999996</v>
+      </c>
+      <c r="F57" s="3">
+        <f>F44-F55</f>
+        <v>32651.595000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="3">
-        <f>C56+C54</f>
+      <c r="C58" s="3">
+        <f>C57+C55</f>
         <v>37798</v>
       </c>
-      <c r="D57" s="3">
-        <f>D56+D54</f>
+      <c r="D58" s="3">
+        <f>D57+D55</f>
         <v>39819</v>
       </c>
-      <c r="E57" s="3">
-        <f>E56+E54</f>
+      <c r="E58" s="3">
+        <f>E57+E55</f>
         <v>51119.067999999999</v>
       </c>
-      <c r="F57" s="3">
-        <f>F56+F54</f>
+      <c r="F58" s="3">
+        <f>F57+F55</f>
         <v>58365.641000000003</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="B60" t="s">
-        <v>117</v>
-      </c>
-      <c r="D60" s="9">
-        <f>D43/C43-1</f>
-        <v>5.3468437483464637E-2</v>
-      </c>
-      <c r="E60" s="9">
-        <f t="shared" ref="E60:F60" si="4">E43/D43-1</f>
-        <v>0.2837858308847534</v>
-      </c>
-      <c r="F60" s="9">
-        <f t="shared" si="4"/>
-        <v>0.14175870733793516</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="B61" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D61" s="9">
-        <f>D39/C39-1</f>
-        <v>3.4064840064060853E-2</v>
+        <f>D44/C44-1</f>
+        <v>5.3468437483464637E-2</v>
       </c>
       <c r="E61" s="9">
-        <f t="shared" ref="E61:F61" si="5">E39/D39-1</f>
-        <v>0.13766919213059858</v>
+        <f t="shared" ref="E61:F61" si="5">E44/D44-1</f>
+        <v>0.2837858308847534</v>
       </c>
       <c r="F61" s="9">
         <f t="shared" si="5"/>
-        <v>0.16061118255742124</v>
+        <v>0.14175870733793516</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="B62" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D62" s="9">
-        <f>D42/C42-1</f>
-        <v>8.3974140864239599E-2</v>
+        <f>D40/C40-1</f>
+        <v>3.4064840064060853E-2</v>
       </c>
       <c r="E62" s="9">
-        <f t="shared" ref="E62:F62" si="6">E42/D42-1</f>
-        <v>0.50292868353317854</v>
+        <f t="shared" ref="E62:F62" si="6">E40/D40-1</f>
+        <v>0.13766919213059858</v>
       </c>
       <c r="F62" s="9">
         <f t="shared" si="6"/>
+        <v>0.16061118255742124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="D63" s="9">
+        <f>D43/C43-1</f>
+        <v>8.3974140864239599E-2</v>
+      </c>
+      <c r="E63" s="9">
+        <f t="shared" ref="E63:F63" si="7">E43/D43-1</f>
+        <v>0.50292868353317854</v>
+      </c>
+      <c r="F63" s="9">
+        <f t="shared" si="7"/>
         <v>0.12035575715458102</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" s="9">
-        <f>D54/C54-1</f>
-        <v>0.10326249625860529</v>
-      </c>
-      <c r="E64" s="9">
-        <f t="shared" ref="E64:F64" si="7">E54/D54-1</f>
-        <v>1.2779626966901794</v>
-      </c>
-      <c r="F64" s="9">
-        <f t="shared" si="7"/>
-        <v>0.53122313449282643</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="B65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D65" s="9">
-        <f>D48/C48-1</f>
-        <v>0.13214285714285712</v>
+        <f>D55/C55-1</f>
+        <v>0.10326249625860529</v>
       </c>
       <c r="E65" s="9">
-        <f t="shared" ref="E65:F65" si="8">E48/D48-1</f>
-        <v>0.77076214511041008</v>
+        <f t="shared" ref="E65:F65" si="8">E55/D55-1</f>
+        <v>1.2779626966901794</v>
       </c>
       <c r="F65" s="9">
         <f t="shared" si="8"/>
-        <v>0.82855873426687543</v>
+        <v>0.53122313449282643</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D66" s="9">
-        <f>D53/C53-1</f>
-        <v>5.4391619661563251E-2</v>
+        <f>D49/C49-1</f>
+        <v>0.13214285714285712</v>
       </c>
       <c r="E66" s="9">
-        <f t="shared" ref="E66:F66" si="9">E53/D53-1</f>
-        <v>2.1995288498280479</v>
+        <f t="shared" ref="E66:F66" si="9">E49/D49-1</f>
+        <v>0.77076214511041008</v>
       </c>
       <c r="F66" s="9">
         <f t="shared" si="9"/>
+        <v>0.82855873426687543</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67" s="9">
+        <f>D54/C54-1</f>
+        <v>5.4391619661563251E-2</v>
+      </c>
+      <c r="E67" s="9">
+        <f t="shared" ref="E67:F67" si="10">E54/D54-1</f>
+        <v>2.1995288498280479</v>
+      </c>
+      <c r="F67" s="9">
+        <f t="shared" si="10"/>
         <v>0.23222539333086267</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" t="s">
+    <row r="69" spans="1:6">
+      <c r="B69" t="s">
         <v>123</v>
       </c>
-      <c r="D68" s="9">
-        <f t="shared" ref="D68:E68" si="10">D56/C56-1</f>
+      <c r="D69" s="9">
+        <f t="shared" ref="D69:E69" si="11">D57/C57-1</f>
         <v>4.2775421005270653E-2</v>
       </c>
-      <c r="E68" s="9">
-        <f t="shared" si="10"/>
+      <c r="E69" s="9">
+        <f t="shared" si="11"/>
         <v>5.7907572348753211E-2</v>
       </c>
-      <c r="F68" s="9">
-        <f>F56/E56-1</f>
+      <c r="F69" s="9">
+        <f>F57/E57-1</f>
         <v>-4.8777473657157011E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="B70" t="s">
+    <row r="71" spans="1:6">
+      <c r="B71" t="s">
         <v>124</v>
       </c>
-      <c r="C70" s="2">
-        <f>C39/C48</f>
+      <c r="C71" s="2">
+        <f>C40/C49</f>
         <v>5.5007142857142854</v>
       </c>
-      <c r="D70" s="2">
-        <f t="shared" ref="D70:F70" si="11">D39/D48</f>
+      <c r="D71" s="2">
+        <f t="shared" ref="D71:F71" si="12">D40/D49</f>
         <v>5.0241850683491061</v>
       </c>
-      <c r="E70" s="2">
-        <f t="shared" si="11"/>
+      <c r="E71" s="2">
+        <f t="shared" si="12"/>
         <v>3.2279098486527396</v>
       </c>
-      <c r="F70" s="2">
-        <f t="shared" si="11"/>
+      <c r="F71" s="2">
+        <f t="shared" si="12"/>
         <v>2.04879843147922</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="27" t="s">
+    <row r="75" spans="1:6">
+      <c r="B75" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="28"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="29"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C75" s="18">
-        <v>1078</v>
-      </c>
-      <c r="D75" s="18">
-        <v>1053</v>
-      </c>
-      <c r="E75" s="18">
-        <v>2307</v>
-      </c>
-      <c r="F75" s="18">
-        <v>-1400</v>
-      </c>
+      <c r="C75" s="33"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="34"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C76" s="8">
-        <v>595</v>
+        <v>148</v>
+      </c>
+      <c r="C76" s="18">
+        <v>1078</v>
       </c>
       <c r="D76" s="18">
-        <v>1623</v>
+        <v>1053</v>
       </c>
       <c r="E76" s="18">
-        <v>-1608</v>
+        <v>2307</v>
       </c>
       <c r="F76" s="18">
-        <v>1444</v>
+        <v>-1400</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" s="8">
+        <v>595</v>
+      </c>
+      <c r="D77" s="18">
+        <v>1623</v>
+      </c>
+      <c r="E77" s="18">
+        <v>-1608</v>
+      </c>
+      <c r="F77" s="18">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="B78" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C77" s="8">
+      <c r="C78" s="8">
         <v>-234</v>
       </c>
-      <c r="D77" s="18">
+      <c r="D78" s="18">
         <v>-3791</v>
       </c>
-      <c r="E77" s="18">
+      <c r="E78" s="18">
         <v>-2743</v>
       </c>
-      <c r="F77" s="18">
+      <c r="F78" s="18">
         <v>-3838</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" s="7" customFormat="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C78" s="7">
-        <v>1439</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-1115</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-1911</v>
-      </c>
-      <c r="F78" s="7">
-        <v>-3794</v>
       </c>
     </row>
     <row r="79" spans="1:6" s="7" customFormat="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C79" s="7">
-        <v>-1104</v>
+        <v>1439</v>
       </c>
       <c r="D79" s="7">
-        <v>-2122</v>
+        <v>-1115</v>
       </c>
       <c r="E79" s="7">
-        <v>-1817</v>
+        <v>-1911</v>
       </c>
       <c r="F79" s="7">
-        <v>-2473</v>
+        <v>-3794</v>
       </c>
     </row>
     <row r="80" spans="1:6" s="7" customFormat="1">
       <c r="A80" s="6"/>
       <c r="B80" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-1104</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-2122</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-1817</v>
+      </c>
+      <c r="F80" s="7">
+        <v>-2473</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" s="7" customFormat="1">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C81" s="6">
         <v>335</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D81" s="7">
         <v>-3237</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E81" s="7">
         <v>-3728</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F81" s="7">
         <v>-6267</v>
       </c>
     </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="8" t="s">
+    <row r="82" spans="1:6">
+      <c r="B82" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C81" s="18">
+      <c r="C82" s="18">
         <v>4022</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D82" s="8">
         <v>-193</v>
       </c>
-      <c r="E81" s="18">
+      <c r="E82" s="18">
         <v>-1126</v>
       </c>
-      <c r="F81" s="18">
+      <c r="F82" s="18">
         <v>6233</v>
       </c>
     </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="8" t="s">
+    <row r="83" spans="1:6">
+      <c r="B83" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C83" s="18">
         <v>4355</v>
       </c>
-      <c r="D82" s="18">
+      <c r="D83" s="18">
         <v>-3414</v>
       </c>
-      <c r="E82" s="18">
+      <c r="E83" s="18">
         <v>-4796</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F83" s="8">
         <v>-22</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" t="s">
+    <row r="85" spans="1:6">
+      <c r="B85" t="s">
         <v>156</v>
       </c>
-      <c r="D84" s="9">
-        <f>C78/D78-1</f>
+      <c r="D85" s="9">
+        <f>C79/D79-1</f>
         <v>-2.2905829596412559</v>
       </c>
-      <c r="E84" s="9">
-        <f>E78/C78-1</f>
+      <c r="E85" s="9">
+        <f>E79/C79-1</f>
         <v>-2.328005559416261</v>
       </c>
-      <c r="F84" s="9">
-        <f>F78/E78-1</f>
+      <c r="F85" s="9">
+        <f>F79/E79-1</f>
         <v>0.9853479853479854</v>
       </c>
     </row>
-    <row r="85" spans="2:6">
-      <c r="B85" t="s">
+    <row r="86" spans="1:6">
+      <c r="B86" t="s">
         <v>157</v>
       </c>
-      <c r="D85" s="9">
-        <f>C80/D80-1</f>
+      <c r="D86" s="9">
+        <f>C81/D81-1</f>
         <v>-1.1034908866234168</v>
       </c>
-      <c r="E85" s="9">
-        <f>E80/C80-1</f>
+      <c r="E86" s="9">
+        <f>E81/C81-1</f>
         <v>-12.128358208955223</v>
       </c>
-      <c r="F85" s="9">
-        <f t="shared" ref="F85" si="12">F80/E80-1</f>
+      <c r="F86" s="9">
+        <f t="shared" ref="F86" si="13">F81/E81-1</f>
         <v>0.68106223175965663</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="5" t="s">
+    <row r="88" spans="1:6">
+      <c r="B88" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="23" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="23" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="5" t="s">
+    <row r="90" spans="1:6">
+      <c r="B90" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="22" t="s">
+    <row r="91" spans="1:6">
+      <c r="B91" s="22" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="91" spans="2:6">
-      <c r="B91" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B75:F75"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{57F4C766-BC37-604C-BD7B-6400956837A5}"/>
@@ -3027,6 +3208,217 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F904BC-0850-CA49-A958-0973EE681FF6}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="24">
+        <f>((Main!K7/(Main!K8+Main!K7))*C4)+((Main!K8/(Main!K8+Main!K7))*C10*(1-C13))</f>
+        <v>6.885039299464453E-2</v>
+      </c>
+      <c r="H2" s="38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="C3" s="25"/>
+      <c r="H3" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="24">
+        <f>C5+C6*(C8)</f>
+        <v>8.7574999999999986E-2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="26">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="25">
+        <v>0.99</v>
+      </c>
+      <c r="D6" s="39"/>
+      <c r="H6" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="26">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="26">
+        <f>C7-C5</f>
+        <v>4.2499999999999996E-2</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="8"/>
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="24">
+        <f>(C11/C12)*(1-C13)</f>
+        <v>1.7264378871663585E-2</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="27">
+        <f>Model!F16</f>
+        <v>510.51299999999998</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="27">
+        <f>Main!K8</f>
+        <v>19576</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="28">
+        <f>Model!E20</f>
+        <v>0.33798457474797627</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="H14" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="41">
+        <f>Main!K21/Main!K22</f>
+        <v>0.78752802121917787</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="H15" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.78339999999999999</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="C17" s="25"/>
+      <c r="H17" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="K21" s="8"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{D1482282-AD9C-744A-BC0C-BCE41CFD5CEB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A87B8C-9BF6-3745-8C7B-319592E2BC8A}">
   <dimension ref="A2:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>

--- a/Models/CDGP.xlsx
+++ b/Models/CDGP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36a87f973740ffce/Documents/Personal/Finance/Models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1028" documentId="8_{AB677FD1-DACE-674B-8687-43CC81DC24D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80B655D2-84CF-754B-B191-140FDA80FC6D}"/>
+  <xr:revisionPtr revIDLastSave="1030" documentId="8_{AB677FD1-DACE-674B-8687-43CC81DC24D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83DF83A7-05AE-8D48-B6A8-E43FB98E4561}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17860" xr2:uid="{D13D7BE5-6829-5F46-8F18-3C3B077CFA17}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{D13D7BE5-6829-5F46-8F18-3C3B077CFA17}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/Models/CDGP.xlsx
+++ b/Models/CDGP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36a87f973740ffce/Documents/Personal/Finance/Models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1030" documentId="8_{AB677FD1-DACE-674B-8687-43CC81DC24D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83DF83A7-05AE-8D48-B6A8-E43FB98E4561}"/>
+  <xr:revisionPtr revIDLastSave="1039" documentId="8_{AB677FD1-DACE-674B-8687-43CC81DC24D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B27D25B-B159-CB46-9362-EC0AD4176992}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{D13D7BE5-6829-5F46-8F18-3C3B077CFA17}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="199">
   <si>
     <t xml:space="preserve">Price </t>
   </si>
@@ -477,9 +477,6 @@
     <t>CFS</t>
   </si>
   <si>
-    <t>Working capital changes</t>
-  </si>
-  <si>
     <t>CapEx</t>
   </si>
   <si>
@@ -634,6 +631,12 @@
   </si>
   <si>
     <t xml:space="preserve">* low WACC &amp; the D/E = industry average </t>
+  </si>
+  <si>
+    <t>ΔNWC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFF </t>
   </si>
 </sst>
 </file>
@@ -813,15 +816,12 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -840,12 +840,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1203,7 +1206,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J3" s="5"/>
     </row>
@@ -1211,15 +1214,15 @@
       <c r="B4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="30"/>
-      <c r="L4" s="31"/>
+      <c r="J4" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="K4" s="40"/>
+      <c r="L4" s="41"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
         <v>0</v>
@@ -1360,12 +1363,12 @@
       </c>
     </row>
     <row r="18" spans="2:13">
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
       <c r="J18" t="s">
         <v>7</v>
       </c>
@@ -1389,7 +1392,7 @@
         <v>24</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K20" s="7">
         <f>Model!F44</f>
@@ -1439,7 +1442,7 @@
         <v>-3.7169406719085057E-2</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K22" s="7">
         <f>K20-K21</f>
@@ -1748,12 +1751,12 @@
       </c>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="31"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="41"/>
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="6" t="s">
@@ -1927,13 +1930,13 @@
       </c>
     </row>
     <row r="3" spans="1:6" customFormat="1">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
     </row>
     <row r="4" spans="1:6" s="7" customFormat="1">
       <c r="A4" s="6"/>
@@ -2240,7 +2243,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="B20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20" s="9">
         <f t="shared" ref="C20:E20" si="1">C19/C18</f>
@@ -2448,13 +2451,13 @@
     </row>
     <row r="36" spans="1:6" s="7" customFormat="1">
       <c r="A36" s="6"/>
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="38"/>
     </row>
     <row r="37" spans="1:6">
       <c r="B37" t="s">
@@ -2983,17 +2986,17 @@
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C75" s="33"/>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="35"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C76" s="18">
         <v>1078</v>
@@ -3010,7 +3013,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C77" s="8">
         <v>595</v>
@@ -3027,7 +3030,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="8" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="C78" s="8">
         <v>-234</v>
@@ -3045,7 +3048,7 @@
     <row r="79" spans="1:6" s="7" customFormat="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C79" s="7">
         <v>1439</v>
@@ -3063,7 +3066,7 @@
     <row r="80" spans="1:6" s="7" customFormat="1">
       <c r="A80" s="6"/>
       <c r="B80" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C80" s="7">
         <v>-1104</v>
@@ -3081,7 +3084,7 @@
     <row r="81" spans="1:6" s="7" customFormat="1">
       <c r="A81" s="6"/>
       <c r="B81" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="6">
         <v>335</v>
@@ -3098,7 +3101,7 @@
     </row>
     <row r="82" spans="1:6">
       <c r="B82" s="8" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="C82" s="18">
         <v>4022</v>
@@ -3115,7 +3118,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C83" s="18">
         <v>4355</v>
@@ -3132,7 +3135,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D85" s="9">
         <f>C79/D79-1</f>
@@ -3149,7 +3152,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D86" s="9">
         <f>C81/D81-1</f>
@@ -3166,32 +3169,32 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="B89" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="B90" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="B93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3225,75 +3228,75 @@
     </row>
     <row r="2" spans="1:8">
       <c r="B2" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C2" s="24">
         <f>((Main!K7/(Main!K8+Main!K7))*C4)+((Main!K8/(Main!K8+Main!K7))*C10*(1-C13))</f>
         <v>6.885039299464453E-2</v>
       </c>
-      <c r="H2" s="38" t="s">
-        <v>177</v>
+      <c r="H2" s="29" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="C3" s="25"/>
       <c r="H3" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C4" s="24">
         <f>C5+C6*(C8)</f>
         <v>8.7574999999999986E-2</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5" s="26">
         <v>4.5499999999999999E-2</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" s="25">
         <v>0.99</v>
       </c>
-      <c r="D6" s="39"/>
+      <c r="D6" s="30"/>
       <c r="H6" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C7" s="26">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="D7" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="26">
         <f>C7-C5</f>
@@ -3308,19 +3311,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C10" s="24">
         <f>(C11/C12)*(1-C13)</f>
         <v>1.7264378871663585E-2</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C11" s="27">
         <f>Model!F16</f>
@@ -3333,7 +3336,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="27">
         <f>Main!K8</f>
@@ -3343,12 +3346,12 @@
         <v>6</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="28">
         <f>Model!E20</f>
@@ -3358,47 +3361,47 @@
         <v>56</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="H14" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="B15" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="41">
+      <c r="B15" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="32">
         <f>Main!K21/Main!K22</f>
         <v>0.78752802121917787</v>
       </c>
-      <c r="D15" s="40"/>
+      <c r="D15" s="31"/>
       <c r="H15" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2">
         <v>0.78339999999999999</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="2:11">
       <c r="C17" s="25"/>
       <c r="H17" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -3566,7 +3569,7 @@
         <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3574,10 +3577,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3585,10 +3588,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3596,10 +3599,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" t="s">
         <v>153</v>
-      </c>
-      <c r="C17" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
